--- a/251211/NMDAR_PsychiatricSymptoms.xlsx
+++ b/251211/NMDAR_PsychiatricSymptoms.xlsx
@@ -383,11 +383,11 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.992</v>
+        <v>0.923</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.9669 – 1.0183</t>
+          <t>0.7146 – 1.1987</t>
         </is>
       </c>
       <c r="D2">
@@ -401,11 +401,11 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.008</v>
+        <v>1.0831</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.9836 – 1.0345</t>
+          <t>0.8474 – 1.4034</t>
         </is>
       </c>
       <c r="D3">
@@ -419,11 +419,11 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.0009</v>
+        <v>1.0093</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.9786 – 1.0251</t>
+          <t>0.8055 – 1.2815</t>
         </is>
       </c>
       <c r="D4">
@@ -437,11 +437,11 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.0104</v>
+        <v>1.1093</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.9882 – 1.0344</t>
+          <t>0.8879 – 1.4031</t>
         </is>
       </c>
       <c r="D5">
@@ -455,11 +455,11 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.9593</v>
+        <v>0.9959</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.122 – 9.026</t>
+          <t>0.8103 – 1.2461</t>
         </is>
       </c>
       <c r="D6">
@@ -473,11 +473,11 @@
         </is>
       </c>
       <c r="B7">
-        <v>1.3118</v>
+        <v>1.0275</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.2037 – 10.819</t>
+          <t>0.8529 – 1.2689</t>
         </is>
       </c>
       <c r="D7">
@@ -491,11 +491,11 @@
         </is>
       </c>
       <c r="B8">
-        <v>1.0699</v>
+        <v>1.0068</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.178 – 7.5922</t>
+          <t>0.8415 – 1.2247</t>
         </is>
       </c>
       <c r="D8">
@@ -509,11 +509,11 @@
         </is>
       </c>
       <c r="B9">
-        <v>1.7401</v>
+        <v>1.057</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.2871 – 12.5697</t>
+          <t>0.8827 – 1.288</t>
         </is>
       </c>
       <c r="D9">
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.9996</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.9717 – 1.0301</t>
+          <t>0.7503 – 1.3453</t>
         </is>
       </c>
       <c r="D10">
@@ -545,11 +545,11 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.0111</v>
+        <v>1.1162</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.9837 – 1.0416</t>
+          <t>0.8481 – 1.5037</t>
         </is>
       </c>
       <c r="D11">
@@ -563,11 +563,11 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.9902</v>
+        <v>0.9065</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.9657 – 1.0168</t>
+          <t>0.7051 – 1.1813</t>
         </is>
       </c>
       <c r="D12">
@@ -581,11 +581,11 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.9982</v>
+        <v>0.9821</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.9741 – 1.0245</t>
+          <t>0.7693 – 1.274</t>
         </is>
       </c>
       <c r="D13">
@@ -599,11 +599,11 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.9879</v>
+        <v>0.8855</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.9681 – 1.0089</t>
+          <t>0.7229 – 1.0923</t>
         </is>
       </c>
       <c r="D14">
@@ -617,11 +617,11 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.9951</v>
+        <v>0.9519</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.9722 – 1.0191</t>
+          <t>0.7544 – 1.2084</t>
         </is>
       </c>
       <c r="D15">
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.0164</v>
+        <v>1.1763</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.9937 – 1.041</t>
+          <t>0.9391 – 1.4944</t>
         </is>
       </c>
       <c r="D16">
@@ -653,11 +653,11 @@
         </is>
       </c>
       <c r="B17">
-        <v>1.0147</v>
+        <v>1.1566</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.9922 – 1.0393</t>
+          <t>0.9251 – 1.4701</t>
         </is>
       </c>
       <c r="D17">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.9916</v>
+        <v>0.9192</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.9705 – 1.0138</t>
+          <t>0.741 – 1.147</t>
         </is>
       </c>
       <c r="D18">
@@ -689,11 +689,11 @@
         </is>
       </c>
       <c r="B19">
-        <v>1.0095</v>
+        <v>1.0992</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.9886 – 1.0325</t>
+          <t>0.8913 – 1.3769</t>
         </is>
       </c>
       <c r="D19">
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.9995000000000001</v>
+        <v>0.9948</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.9799 – 1.0206</t>
+          <t>0.8166 – 1.2259</t>
         </is>
       </c>
       <c r="D20">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.0071</v>
+        <v>1.0734</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.9878 – 1.028</t>
+          <t>0.8848 – 1.3175</t>
         </is>
       </c>
       <c r="D21">
@@ -743,11 +743,11 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.999</v>
+        <v>0.9903</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.9677 – 1.0328</t>
+          <t>0.7205 – 1.3812</t>
         </is>
       </c>
       <c r="D22">
@@ -761,11 +761,11 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.0108</v>
+        <v>1.1139</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.9806 – 1.0441</t>
+          <t>0.8219 – 1.539</t>
         </is>
       </c>
       <c r="D23">
@@ -779,11 +779,11 @@
         </is>
       </c>
       <c r="B24">
-        <v>1.005</v>
+        <v>1.0513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.9778 – 1.0352</t>
+          <t>0.7992 – 1.4134</t>
         </is>
       </c>
       <c r="D24">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="B25">
-        <v>1.013</v>
+        <v>1.1384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.9859 – 1.0431</t>
+          <t>0.8678 – 1.5246</t>
         </is>
       </c>
       <c r="D25">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.9921</v>
+        <v>0.924</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.971 – 1.0143</t>
+          <t>0.7453 – 1.1526</t>
         </is>
       </c>
       <c r="D26">
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.0107</v>
+        <v>1.1123</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.9897 – 1.0338</t>
+          <t>0.9016 – 1.3947</t>
         </is>
       </c>
       <c r="D27">
@@ -851,11 +851,11 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.999</v>
+        <v>0.9897</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.9796 – 1.0199</t>
+          <t>0.8134 – 1.218</t>
         </is>
       </c>
       <c r="D28">
@@ -869,11 +869,11 @@
         </is>
       </c>
       <c r="B29">
-        <v>1.0074</v>
+        <v>1.0764</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.9881 – 1.0283</t>
+          <t>0.8872 – 1.3213</t>
         </is>
       </c>
       <c r="D29">
